--- a/AAII_Financials/Yearly/WPC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WPC_YR_FIN.xlsx
@@ -1008,10 +1008,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-121200</v>
+        <v>-17800</v>
       </c>
       <c r="E14" s="3">
-        <v>-69300</v>
+        <v>64700</v>
       </c>
       <c r="F14" s="3">
         <v>-224600</v>
@@ -1251,10 +1251,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>232800</v>
+        <v>129400</v>
       </c>
       <c r="E20" s="3">
-        <v>136100</v>
+        <v>2100</v>
       </c>
       <c r="F20" s="3">
         <v>14700</v>
@@ -1302,10 +1302,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1178400</v>
+        <v>1281800</v>
       </c>
       <c r="E21" s="3">
-        <v>1148400</v>
+        <v>1282400</v>
       </c>
       <c r="F21" s="3">
         <v>1393800</v>
@@ -1863,10 +1863,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-232800</v>
+        <v>-129400</v>
       </c>
       <c r="E32" s="3">
-        <v>-136100</v>
+        <v>-2100</v>
       </c>
       <c r="F32" s="3">
         <v>-14700</v>
